--- a/lab03/dados/rotulagem/avaliador_3.xlsx
+++ b/lab03/dados/rotulagem/avaliador_3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="repositorios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="releases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="repositorios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="releases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,6 +476,16 @@
           <t>https://github.com/tldraw/tldraw</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,6 +498,16 @@
           <t>https://github.com/babel/babel</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,6 +520,21 @@
           <t>https://github.com/tw93/Pake</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CLI como interface principal de empacotamento; releases com binarios anexados</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,6 +547,16 @@
           <t>https://github.com/firecrawl/firecrawl</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -524,6 +569,21 @@
           <t>https://github.com/sickn33/agentic-awesome-skills</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>colecao/catalogo de skills (playbooks) com CLI auxiliar; sem modo de uso dominante de biblioteca ou app</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -536,6 +596,16 @@
           <t>https://github.com/gogs/gogs</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -548,6 +618,16 @@
           <t>https://github.com/prettier/prettier</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -560,6 +640,21 @@
           <t>https://github.com/headroomlabs-ai/headroom</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>biblioteca (compress) com proxy e servidor MCP; README lista Library primeiro</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -572,6 +667,16 @@
           <t>https://github.com/anomalyco/opencode</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -584,6 +689,16 @@
           <t>https://github.com/jamiepine/voicebox</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -596,6 +711,16 @@
           <t>https://github.com/serverless/serverless</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -608,6 +733,16 @@
           <t>https://github.com/paperclipai/paperclip</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -620,6 +755,21 @@
           <t>https://github.com/JuliaLang/julia</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>linguagem/compilador invocado por linha de comando e REPL (julia); instaladores anexados</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -632,6 +782,16 @@
           <t>https://github.com/axios/axios</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -644,6 +804,16 @@
           <t>https://github.com/debpalash/VoiceStudio</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -656,6 +826,16 @@
           <t>https://github.com/HKUDS/nanobot</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -668,6 +848,16 @@
           <t>https://github.com/facebookresearch/faiss</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -680,6 +870,16 @@
           <t>https://github.com/Homebrew/brew</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -692,6 +892,16 @@
           <t>https://github.com/coollabsio/coolify</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -704,6 +914,16 @@
           <t>https://github.com/heygen-com/hyperframes</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -716,6 +936,16 @@
           <t>https://github.com/OpenHands/OpenHands</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -728,6 +958,21 @@
           <t>https://github.com/toeverything/AFFiNE</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>84 das 100 releases sao builds canary/pre-release diarias sem notas; as versoes estaveis com notas sao minoria</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -740,6 +985,16 @@
           <t>https://github.com/jestjs/jest</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -752,6 +1007,16 @@
           <t>https://github.com/getsentry/sentry</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -764,6 +1029,16 @@
           <t>https://github.com/redis/redis</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -776,6 +1051,21 @@
           <t>https://github.com/supabase/supabase</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>as 'releases' sao boletins mensais (Developer Update) com anuncios de produto, sem relacao com uma versao instalada</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -788,6 +1078,16 @@
           <t>https://github.com/exelban/stats</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -800,6 +1100,21 @@
           <t>https://github.com/llvm/llvm-project</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>infraestrutura/toolkit de compiladores (bibliotecas e ferramentas); README apresenta o toolkit para construir compiladores</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -812,6 +1127,16 @@
           <t>https://github.com/makeplane/plane</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -824,6 +1149,21 @@
           <t>https://github.com/microsoft/monaco-editor</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>94 das 100 releases sao builds dev diarios (v0.56.0-dev-AAAAMMDD) sem notas; versoes estaveis sao minoria</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -836,6 +1176,16 @@
           <t>https://github.com/langchain-ai/langchain</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -848,6 +1198,16 @@
           <t>https://github.com/crewAIInc/crewAI</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -860,6 +1220,21 @@
           <t>https://github.com/rust-lang/rust</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>compilador/toolchain (rustc, cargo) invocado por linha de comando; README descreve compilador, std e docs</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -872,6 +1247,21 @@
           <t>https://github.com/ggml-org/llama.cpp</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>README apresenta primeiro 'llama cli'/'llama serve'. Releases bNNNN sao uma por commit, todas pre-release, com binarios (sugere 'nao'), mas ha binarios instalaveis e tambem releases curadas (v0.4.1): evidencia conflitante</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -884,6 +1274,16 @@
           <t>https://github.com/metabase/metabase</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -896,6 +1296,21 @@
           <t>https://github.com/cline/cline</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>README apresenta primeiro a CLI (npm i -g cline); tambem ha app desktop e extensao VS Code; releases por componente com notas</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -908,6 +1323,16 @@
           <t>https://github.com/yt-dlp/yt-dlp</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -920,6 +1345,21 @@
           <t>https://github.com/rtk-ai/rtk</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>94 das 100 releases sao builds dev-X.Y.Z-rc.N automaticos, sem notas; as versoes estaveis sao minoria</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -932,6 +1372,16 @@
           <t>https://github.com/denoland/deno</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -944,6 +1394,21 @@
           <t>https://github.com/modelcontextprotocol/servers</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>colecao de implementacoes de referencia (educacionais) de servidores MCP; sem modo de uso dominante. Releases CalVer publicam pacotes atualizados</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -956,6 +1421,16 @@
           <t>https://github.com/opendatalab/MinerU</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -968,6 +1443,16 @@
           <t>https://github.com/astral-sh/uv</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -980,6 +1465,21 @@
           <t>https://github.com/tinyhumansai/openhuman</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>app desktop (README: 'A desktop app for people. A Rust library for developers'), instaladores anexados</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -992,6 +1492,16 @@
           <t>https://github.com/microsoft/playwright</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1004,6 +1514,16 @@
           <t>https://github.com/bitcoin/bitcoin</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1016,6 +1536,16 @@
           <t>https://github.com/puppeteer/puppeteer</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1028,6 +1558,21 @@
           <t>https://github.com/vectorize-io/hindsight</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>sistema de memoria para agentes iniciado como servidor (docker run) com CLI e clientes; releases com imagens e notas</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1040,6 +1585,21 @@
           <t>https://github.com/abhigyanpatwari/GitNexus</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>as 100 releases mais recentes sao todas release candidates automaticas (rc.N, pre-release); as versoes estaveis curadas (ex.: v1.4.10, v1.6.11) ficam fora da janela, entao nao da para ver o predominio</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1052,6 +1612,21 @@
           <t>https://github.com/openbq-org/OpenBB</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>pip install openbb: plataforma/biblioteca Python; README apresenta primeiro o pacote Python</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1064,6 +1639,16 @@
           <t>https://github.com/MHSanaei/3x-ui</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1076,6 +1661,16 @@
           <t>https://github.com/TryGhost/Ghost</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1088,6 +1683,16 @@
           <t>https://github.com/usememos/memos</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1100,6 +1705,21 @@
           <t>https://github.com/jgm/pandoc</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>README apresenta primeiro a biblioteca Haskell e depois a ferramenta de linha de comando que a usa</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1112,6 +1732,16 @@
           <t>https://github.com/mermaid-js/mermaid</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1124,6 +1754,16 @@
           <t>https://github.com/outline/outline</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1136,6 +1776,16 @@
           <t>https://github.com/agno-agi/agno</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1148,6 +1798,16 @@
           <t>https://github.com/coder/code-server</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1160,6 +1820,16 @@
           <t>https://github.com/spring-projects/spring-boot</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1172,6 +1842,16 @@
           <t>https://github.com/ionic-team/ionic-framework</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1182,6 +1862,16 @@
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>https://github.com/harry0703/MoneyPrinterTurbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -1330,6 +2020,11 @@
           <t>https://github.com/tldraw/tldraw/compare/v3.15.6...v4.3.2</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1352,6 +2047,11 @@
           <t>https://github.com/tldraw/tldraw/compare/v4.5.8...v4.5.9</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1374,6 +2074,11 @@
           <t>https://github.com/tldraw/tldraw/compare/v5.2.1...v5.2.2</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1396,6 +2101,11 @@
           <t>https://github.com/tldraw/tldraw/compare/v5.2.4...v5.2.5</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1418,6 +2128,11 @@
           <t>https://github.com/tldraw/tldraw/compare/v5.3.1...v5.3.2</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1440,6 +2155,11 @@
           <t>https://github.com/babel/babel/compare/v7.28.4...v7.28.5</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1462,6 +2182,11 @@
           <t>https://github.com/babel/babel/compare/v7.28.5...v7.28.6</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1484,6 +2209,11 @@
           <t>https://github.com/babel/babel/compare/v7.29.2...v7.29.3</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1506,6 +2236,11 @@
           <t>https://github.com/babel/babel/compare/v7.29.5...v7.29.6</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1528,6 +2263,11 @@
           <t>https://github.com/babel/babel/compare/v8.0.0...v8.0.1</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1550,6 +2290,11 @@
           <t>https://github.com/tw93/Pake/compare/V3.3.5...V3.4.0</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1572,6 +2317,16 @@
           <t>https://github.com/tw93/Pake/compare/V3.4.0...V3.4.3</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>mistura otimizacao de empacotamento/proxy com opcao nova (--maximize)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1594,6 +2349,11 @@
           <t>https://github.com/tw93/Pake/compare/V3.10.0...V3.11.0</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1616,6 +2376,11 @@
           <t>https://github.com/tw93/Pake/compare/V3.13.1...V3.14.0</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1638,6 +2403,11 @@
           <t>https://github.com/tw93/Pake/compare/V3.15.1...V3.15.6</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1660,6 +2430,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.3.0...v2.4.0</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,6 +2457,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.4.0...v2.5.0</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1704,6 +2484,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.5.0...v2.6.0</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1726,6 +2511,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.8.0...v2.9.0</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1748,6 +2538,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.10...v2.11.0</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1770,6 +2565,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v2.9.0...v2.10.0</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1792,6 +2592,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v13.7.0...v13.8.0</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1814,6 +2619,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v13.11.0...v13.12.0</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1836,6 +2646,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v15.4.0...v15.5.0</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1858,6 +2673,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v18.3.0...v18.4.0</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1880,6 +2700,11 @@
           <t>https://github.com/gogs/gogs/compare/v0.13.3...v0.13.4</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1902,6 +2727,16 @@
           <t>https://github.com/gogs/gogs/compare/v0.13.4...v0.14.0</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>release retirada; notas sem lista de mudancas; 308 commits mistos, sem evidencia de predominio de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1924,6 +2759,11 @@
           <t>https://github.com/gogs/gogs/compare/v0.14.0...v0.14.1</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1946,6 +2786,11 @@
           <t>https://github.com/gogs/gogs/compare/v0.14.1...v0.14.2</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1968,6 +2813,11 @@
           <t>https://github.com/gogs/gogs/compare/v0.14.2...v0.14.3</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1990,6 +2840,16 @@
           <t>https://github.com/prettier/prettier/compare/3.6.2...3.7.0</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>notas so apontam para o blog da versao minor; commits sao majoritariamente deps/chore</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2012,6 +2872,11 @@
           <t>https://github.com/prettier/prettier/compare/3.7.0...3.7.1</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2034,6 +2899,11 @@
           <t>https://github.com/prettier/prettier/compare/3.8.2...3.8.3</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2056,6 +2926,16 @@
           <t>https://github.com/prettier/prettier/compare/3.9.4...3.9.5</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>sem notas; commits mistos (testes, decorators, plugins), sem predominio de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2078,6 +2958,11 @@
           <t>https://github.com/prettier/prettier/compare/3.9.6...3.9.7</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2100,6 +2985,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.13.4...v0.13.5</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2122,6 +3012,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.18.1...v0.18.2</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2144,6 +3039,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.21.31...v0.21.32</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2166,6 +3066,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.25.0...v0.26.0</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2188,6 +3093,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.29.0...v0.30.0</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2210,6 +3120,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v0.15.24...v0.15.26</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2232,6 +3147,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.0.16...v1.0.17</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2254,6 +3174,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.0.24...v1.0.25</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2276,6 +3201,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.0.33...v1.0.34</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2298,6 +3228,16 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.1.57...v1.1.58</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>mistura correcoes com recursos novos (placeholders) e revert</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2315,6 +3255,16 @@
           <t>https://github.com/jamiepine/voicebox/releases/tag/v0.1.1</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>primeira release do repositorio</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2337,6 +3287,11 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.1.7...v0.1.8</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2359,6 +3314,11 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.1.10...v0.1.11</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2381,6 +3341,11 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.2.2...v0.2.3</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2403,6 +3368,11 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.4.4...v0.4.5</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2425,6 +3395,11 @@
           <t>https://github.com/serverless/serverless/compare/v4.21.0...v4.21.1</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2447,6 +3422,11 @@
           <t>https://github.com/serverless/serverless/compare/v4.29.0...sf-core@4.29.3</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2469,6 +3449,11 @@
           <t>https://github.com/serverless/serverless/compare/sf-core@4.29.3...sf-core@4.29.4</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2491,6 +3476,11 @@
           <t>https://github.com/serverless/serverless/compare/sf-core@4.31.0...sf-core@4.31.1</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2513,6 +3503,11 @@
           <t>https://github.com/serverless/serverless/compare/sf-core@4.33.3...sf-core@4.34.0</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2530,6 +3525,16 @@
           <t>https://github.com/paperclipai/paperclip/releases/tag/v0.3.0</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>primeira release do repositorio</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2552,6 +3557,11 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.428.0...v2026.512.0</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2574,6 +3584,11 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.517.0...v2026.525.0</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2596,6 +3611,11 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.626.0...v2026.707.0</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2618,6 +3638,11 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.831.1...v2026.916.0</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2640,6 +3665,11 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.11.7...v1.12.0</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +3692,11 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.3...v1.12.4</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2684,6 +3719,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.10.11...v1.12.6</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>notas so com link; lista de commits inconsistente (comparacao com 4321 commits), sem evidencia de correcao predominante</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2706,6 +3751,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.7...v1.10.12</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>notas so com link; lista de commits inconsistente (722 commits), sem evidencia</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2728,6 +3783,11 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.10.12...v1.13.0</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2750,6 +3810,16 @@
           <t>https://github.com/axios/axios/compare/v0.30.2...v1.13.0</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>mistura correcoes com funcionalidade nova (HTTP2)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2772,6 +3842,11 @@
           <t>https://github.com/axios/axios/compare/v1.13.6...v1.14.0</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2794,6 +3869,11 @@
           <t>https://github.com/axios/axios/compare/v0.31.0...v1.15.1</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2816,6 +3896,11 @@
           <t>https://github.com/axios/axios/compare/v0.32.0...v1.16.1</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2838,6 +3923,11 @@
           <t>https://github.com/axios/axios/compare/v1.17.0...v0.33.0</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2860,6 +3950,11 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.2.4...v0.2.6</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2882,6 +3977,11 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.2.7...v0.3.0</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2904,6 +4004,11 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.3.4...v0.3.5</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2926,6 +4031,11 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.3.15...v0.3.16</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2948,6 +4058,11 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.3.16...v0.3.17</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2965,6 +4080,16 @@
           <t>https://github.com/HKUDS/nanobot/releases/tag/v0.1.3.post4</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>primeira release do repositorio</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2987,6 +4112,11 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.1.3.post4...v0.1.3.post5</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3009,6 +4139,16 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.1.4.post3...v0.1.4.post4</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>mistura funcionalidades e correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3031,6 +4171,11 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.1.5.post3...v0.2.0</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3053,6 +4198,16 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.2.1...v0.2.2</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>release grande (140 PRs) com mistura de refactors, correcoes e recursos; sem predominio claro de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3075,6 +4230,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.12.0...v1.13.0</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3097,6 +4257,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.13.0...v1.13.1</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3119,6 +4284,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.1...v1.14.2</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3141,6 +4311,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.3...v1.15.0</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3163,6 +4338,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.15.0...v1.15.1</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>notas so com link; commits misturam correcoes com recursos e otimizacoes</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3185,6 +4370,11 @@
           <t>https://github.com/Homebrew/brew/compare/4.6.15...4.6.16</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3207,6 +4397,16 @@
           <t>https://github.com/Homebrew/brew/compare/4.6.19...4.6.20</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>mistura melhorias, novo comando e fixes</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3229,6 +4429,11 @@
           <t>https://github.com/Homebrew/brew/compare/5.0.16...5.1.0</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3251,6 +4456,16 @@
           <t>https://github.com/Homebrew/brew/compare/6.0.8...6.0.9</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>mistura correcoes com perf/CI, sem predominio claro</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3273,6 +4488,16 @@
           <t>https://github.com/Homebrew/brew/compare/6.0.14...6.0.15</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>refatoracao de workflows/actions</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3295,6 +4520,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.0.0-beta.432...v4.0.0-beta.433</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3317,6 +4547,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.0.0-beta.436...v4.0.0-beta.437</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3339,6 +4574,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.0.0-beta.454...v4.0.0-beta.455</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3361,6 +4601,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.3.2...v4.3.3</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3383,6 +4628,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.3.7...v4.3.8</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3405,6 +4655,16 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.4.11...v0.4.12</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>mistura feat e fix</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3427,6 +4687,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.4.20...v0.4.21</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3449,6 +4714,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.5.2...v0.5.3</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3471,6 +4741,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.7.21...v0.7.22</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3493,6 +4768,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.7.61...v0.7.62</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3515,6 +4795,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/0.57.2...0.58.0</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3537,6 +4822,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/1.0.2-cli...0.60.0</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3559,6 +4849,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/v1.6.1...v1.7.0</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3581,6 +4876,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/v1.18.0...v1.19.0</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3603,6 +4903,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/v1.22.0...v1.23.0</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3625,6 +4930,11 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.24.1...v0.25.0</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3647,6 +4957,11 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.25.7...v0.26.0</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3669,6 +4984,11 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.26.3...v0.27.0</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3691,6 +5011,11 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.27.0...v0.27.2</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3713,6 +5038,16 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.27.2...v0.27.3</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>mistura melhorias e correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3735,6 +5070,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.2.0...v30.3.0</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3757,6 +5097,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.3.0...v30.4.0</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3779,6 +5124,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.4.0...v30.4.1</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3801,6 +5151,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.4.2...v30.5.0</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3823,6 +5178,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.5.0...v30.5.1</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3845,6 +5205,16 @@
           <t>https://github.com/getsentry/sentry/compare/25.9.0...25.10.0</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>mistura/ so funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3867,6 +5237,16 @@
           <t>https://github.com/getsentry/sentry/compare/25.10.0...25.11.0</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>mistura/ so funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3889,6 +5269,16 @@
           <t>https://github.com/getsentry/sentry/compare/26.2.1...26.3.0</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>mistura/ so funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3911,6 +5301,16 @@
           <t>https://github.com/getsentry/sentry/compare/26.4.2...26.5.0</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>mistura/ so funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3933,6 +5333,16 @@
           <t>https://github.com/getsentry/sentry/compare/26.5.1...26.5.2</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>mistura/ so funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3955,6 +5365,11 @@
           <t>https://github.com/redis/redis/compare/8.2.4...8.4.1</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3977,6 +5392,11 @@
           <t>https://github.com/redis/redis/compare/7.4.8...7.2.13</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3999,6 +5419,11 @@
           <t>https://github.com/redis/redis/compare/7.2.16...7.4.11</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4021,6 +5446,11 @@
           <t>https://github.com/redis/redis/compare/8.2.9...8.4.6</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4043,6 +5473,11 @@
           <t>https://github.com/redis/redis/compare/8.10.1...8.2.10</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4065,6 +5500,16 @@
           <t>https://github.com/supabase/supabase/compare/1.25.04...1.25.12</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>boletim mensal de novidades de produto, nao e release de versao</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4087,6 +5532,16 @@
           <t>https://github.com/supabase/supabase/compare/1.25.12...v1.26.01</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>boletim mensal de novidades de produto, nao e release de versao</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4109,6 +5564,16 @@
           <t>https://github.com/supabase/supabase/compare/v1.26.01...v1.26.02</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>boletim mensal de novidades de produto, nao e release de versao</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4131,6 +5596,16 @@
           <t>https://github.com/supabase/supabase/compare/v1.26.04...v1.26.05</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>boletim mensal de novidades de produto, nao e release de versao</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4153,6 +5628,16 @@
           <t>https://github.com/supabase/supabase/compare/v1.26.07...v1.26.08</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>boletim mensal de novidades de produto, nao e release de versao</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4175,6 +5660,11 @@
           <t>https://github.com/exelban/stats/compare/v2.12.0...v2.12.1</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4197,6 +5687,11 @@
           <t>https://github.com/exelban/stats/compare/v2.12.4...v2.12.5</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4219,6 +5714,11 @@
           <t>https://github.com/exelban/stats/compare/v3.0.14...v3.0.15</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4241,6 +5741,11 @@
           <t>https://github.com/exelban/stats/compare/v3.0.15...v3.0.16</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4263,6 +5768,11 @@
           <t>https://github.com/exelban/stats/compare/v3.0.17...v3.0.18</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4285,6 +5795,11 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.2...llvmorg-21.1.3</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4307,6 +5822,11 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.3...llvmorg-21.1.4</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4329,6 +5849,11 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.5...llvmorg-21.1.6</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4351,6 +5876,11 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.7...llvmorg-21.1.8</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4373,6 +5903,11 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-22.1.1...llvmorg-22.1.2</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4395,6 +5930,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.0.0...v1.1.0</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4417,6 +5957,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.1.0...v1.2.0</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4439,6 +5984,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.2.3...v1.3.0</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4461,6 +6011,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.3.1...v1.4.0</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4483,6 +6038,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.4.0...v1.4.1</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4505,6 +6065,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.53.0...v0.54.0</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>manutencao de build/dependencias; sem predominio de correcao de defeito</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4527,6 +6097,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.54.0...v0.55.0</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>correcoes de CI/website e bump de dependencias, nao de defeito do produto</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4549,6 +6129,11 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.55.0...v0.55.1</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4571,6 +6156,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.55.1...v0.56.0</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>bumps de dependencias e ajustes de pipeline; sem evidencia de correcao predominante</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4593,6 +6188,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.56.0...v0.57.0</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>bumps de dependencias e preparo de release; sem evidencia de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4615,6 +6220,16 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-core%3D%3D1.0.0rc3...langchain%3D%3D1.0.0rc2</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>release candidata inicial; mistura chore/feat/fix</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4637,6 +6252,11 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-anthropic%3D%3D1.0.0...langchain-text-splitters%3D%3D1.0.0</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4659,6 +6279,16 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-groq%3D%3D1.1.2...langchain-anthropic%3D%3D1.3.2</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>mistura suporte a novos recursos (output_config, compaction) e chores</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4681,6 +6311,11 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-perplexity%3D%3D1.3.1...langchain-anthropic%3D%3D1.4.4</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4703,6 +6338,11 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain%3D%3D1.3.16...langchain-fireworks%3D%3D1.6.0</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4725,6 +6365,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/0.201.1...0.203.0</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4747,6 +6392,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.2.0...1.2.1</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4769,6 +6419,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.11...1.15.12</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4791,6 +6446,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.17...1.15.18</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4813,6 +6473,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.18...1.15.19</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4835,6 +6500,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.90.0...1.91.0</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4857,6 +6527,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.93.1...1.94.0</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4879,6 +6554,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.96.0...1.96.1</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4901,6 +6581,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.97.0...1.97.1</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4923,6 +6608,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.97.1...1.98.0</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4945,6 +6635,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b7077...b7078</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4967,6 +6662,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b7219...b7220</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4989,6 +6689,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9128...b9129</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5011,6 +6716,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9753...b9754</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5033,6 +6743,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/v0.4.0...v0.4.1</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5055,6 +6770,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.56.18...v0.56.19</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>notas sem lista de mudancas; commits misturam correcoes com CI/otimizacao/UX ou comparacao inflada, sem predominio de correcao comprovado</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5077,6 +6802,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.54.23...v0.55.23</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>notas sem lista de mudancas; commits misturam correcoes com CI/otimizacao/UX ou comparacao inflada, sem predominio de correcao comprovado</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5099,6 +6834,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.61.2...v0.60.7</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>notas sem lista de mudancas; commits misturam correcoes com CI/otimizacao/UX ou comparacao inflada, sem predominio de correcao comprovado</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5121,6 +6866,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.62.2...v0.58.18</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>notas sem lista de mudancas; commits misturam correcoes com CI/otimizacao/UX ou comparacao inflada, sem predominio de correcao comprovado</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5143,6 +6898,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.59.19...v0.58.22</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>notas sem lista de mudancas; commits misturam correcoes com CI/otimizacao/UX ou comparacao inflada, sem predominio de correcao comprovado</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5165,6 +6930,11 @@
           <t>https://github.com/cline/cline/compare/v3.44.0...v3.44.1</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5187,6 +6957,11 @@
           <t>https://github.com/cline/cline/compare/v4.1.6...desktop-v0.0.10</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5209,6 +6984,16 @@
           <t>https://github.com/cline/cline/compare/v4.1.7...desktop-v0.0.11</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>mistura recursos (colar imagens) e correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5231,6 +7016,16 @@
           <t>https://github.com/cline/cline/compare/sdk/sdk/v0.0.79...cli-v3.0.58</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>mistura ajustes de UI, limite de log e catalogo de modelos</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5253,6 +7048,11 @@
           <t>https://github.com/cline/cline/compare/cli-v3.0.61...desktop-v0.0.22</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5275,6 +7075,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2025.09.26...2025.10.14</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>mistura novos extratores e correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5297,6 +7107,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.01.29...2026.01.31</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>mistura novos suportes e correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5319,6 +7139,11 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.03.03...2026.03.13</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5341,6 +7166,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.03.17...2026.06.09</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>mistura novos recursos, build e correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5363,6 +7198,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.06.09...2026.07.04</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>mistura novos recursos e correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5380,6 +7225,16 @@
           <t>https://github.com/rtk-ai/rtk/releases/tag/v0.2.0</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>primeira release do repositorio</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5402,6 +7257,11 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.8.0...v0.8.1</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5424,6 +7284,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.13.0...v0.13.1</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>corrige o workflow de CI que nao anexava artefatos, nao defeito do produto</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5446,6 +7316,11 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.39.0...v0.40.0</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5468,6 +7343,11 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.44.1...v0.44.2</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5490,6 +7370,11 @@
           <t>https://github.com/denoland/deno/compare/v2.7.6...v2.7.7</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5512,6 +7397,11 @@
           <t>https://github.com/denoland/deno/compare/v2.7.7...v2.7.8</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5534,6 +7424,11 @@
           <t>https://github.com/denoland/deno/compare/v2.8.1...v2.8.2</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5556,6 +7451,11 @@
           <t>https://github.com/denoland/deno/compare/v2.8.3...v2.9.0</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5578,6 +7478,16 @@
           <t>https://github.com/denoland/deno/compare/v2.9.0...v2.9.1</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>mistura feats e fixes</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5600,6 +7510,16 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2025.9.25...2025.11.25</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>notas so listam pacotes; commits mistos (feat/docs/fix)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5622,6 +7542,11 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2025.11.25...2025.12.18</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5644,6 +7569,11 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2025.12.18...2026.1.14</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5666,6 +7596,11 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2026.7.4...2026.7.10</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5688,6 +7623,11 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2026.8.18...2026.8.31</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5710,6 +7650,11 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-2.5.4-released...mineru-2.6.2-released</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5732,6 +7677,11 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-2.6.6-released...mineru-2.6.7-released</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5754,6 +7704,11 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-3.4.4-released...mineru-3.4.5-released</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5776,6 +7731,11 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-4.0.4-released...mineru-4.0.5-released</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5798,6 +7758,11 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-4.0.5-released...mineru-4.0.6-released</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5820,6 +7785,11 @@
           <t>https://github.com/astral-sh/uv/compare/0.10.12...0.11.0</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5842,6 +7812,11 @@
           <t>https://github.com/astral-sh/uv/compare/0.11.9...0.11.10</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5864,6 +7839,11 @@
           <t>https://github.com/astral-sh/uv/compare/0.11.20...0.11.21</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5886,6 +7866,11 @@
           <t>https://github.com/astral-sh/uv/compare/0.11.21...0.11.22</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5908,6 +7893,11 @@
           <t>https://github.com/astral-sh/uv/compare/0.12.4...0.12.5</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5925,6 +7915,16 @@
           <t>https://github.com/tinyhumansai/openhuman/releases/tag/v0.49.32</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>primeira release do repositorio</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5947,6 +7947,16 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.51.5...v0.51.6</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>mistura features e fixes</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5969,6 +7979,16 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.52.6...v0.52.7</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>notas so com link e commit unico de release, sem evidencia de correcao</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5991,6 +8011,16 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.53.22...v0.53.35</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>mistura</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6013,6 +8043,11 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.57.53...v0.58.0</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6035,6 +8070,11 @@
           <t>https://github.com/microsoft/playwright/compare/v1.55.1...v1.56.0</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6057,6 +8097,11 @@
           <t>https://github.com/microsoft/playwright/compare/v1.58.1...v1.58.2</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6079,6 +8124,11 @@
           <t>https://github.com/microsoft/playwright/compare/v1.60.0...v1.61.0</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6101,6 +8151,11 @@
           <t>https://github.com/microsoft/playwright/compare/v1.61.1...v1.62.0</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6123,6 +8178,11 @@
           <t>https://github.com/microsoft/playwright/compare/v1.62.0...v1.62.1</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6145,6 +8205,11 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v29.1...v30.0</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6167,6 +8232,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v29.2...v28.3</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>notas so apontam para release notes externas; comparacao com 197 commits inconsistente (inclui bump para 28.0rc1), sem evidencia</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6189,6 +8264,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v30.2...v29.3</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>idem: notas externas e commits inconsistentes</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6211,6 +8296,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v31.1...v30.3</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>notas externas; commits inconsistentes (inclui bump para 30.0rc1)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6233,6 +8328,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v30.3...v29.4</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>notas externas; commits inconsistentes (inclui bump para 29.0rc1)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6255,6 +8360,11 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-v24.28.0...puppeteer-core-v24.28.0</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6277,6 +8387,11 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-core-v24.32.0...browsers-v2.11.0</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6299,6 +8414,16 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-core-v24.34.0...puppeteer-v24.35.0</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>sincronizacao de versoes/dependencias</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6321,6 +8446,16 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-core-v24.37.2...puppeteer-v24.37.3</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>sincronizacao de versoes/dependencias</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6343,6 +8478,11 @@
           <t>https://github.com/puppeteer/puppeteer/compare/browsers-v3.2.0...puppeteer-v25.7.0</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6360,6 +8500,16 @@
           <t>https://github.com/vectorize-io/hindsight/releases/tag/v0.0.16</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>primeira release do repositorio</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6382,6 +8532,11 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.1.0...v0.1.1</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6404,6 +8559,11 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.3.0...v0.4.0</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6426,6 +8586,16 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.5.3...v0.5.4</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>mistura docs/features/fixes</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6448,6 +8618,11 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.6.2...v0.7.0</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6465,6 +8640,16 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/releases/tag/v1.3.10</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>primeira release do repositorio</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6487,6 +8672,11 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.4.9...v1.4.10</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6509,6 +8699,11 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.5.1...v1.5.2</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6531,6 +8726,11 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.6.2...v1.6.3</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6553,6 +8753,11 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.6.10...v1.6.11</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6575,6 +8780,11 @@
           <t>https://github.com/openbq-org/OpenBB/compare/4.4.5...v4.5.0</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6597,6 +8807,16 @@
           <t>https://github.com/openbq-org/OpenBB/compare/v4.5.0...Open-Data-Platform-v1.0.0</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>primeira versao do app desktop (feature)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6619,6 +8839,11 @@
           <t>https://github.com/openbq-org/OpenBB/compare/v4.7.0...Open-Data-Platform-v1.0.2</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6641,6 +8866,16 @@
           <t>https://github.com/openbq-org/OpenBB/compare/Open-Data-Platform-v2.0.0...ODP</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>release-ponteiro 'latest' para o auto-updater, sem mudancas</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6663,6 +8898,11 @@
           <t>https://github.com/openbq-org/OpenBB/compare/ODP...openbb-v5.0.0</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6685,6 +8925,11 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v2.8.8...v2.8.9</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6707,6 +8952,11 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v2.9.4...v3.1.0</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6729,6 +8979,11 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v3.2.0...v3.2.5</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6751,6 +9006,11 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v3.3.1...v3.4.0</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6773,6 +9033,11 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v3.5.0...v3.6.0</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6795,6 +9060,11 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.10.1...v6.10.2</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6817,6 +9087,11 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.19.3...v6.19.4</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6839,6 +9114,11 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.37.1...v6.38.0</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6861,6 +9141,11 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.52.1...v6.53.0</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6883,6 +9168,11 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.63.0...v6.64.0</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6905,6 +9195,11 @@
           <t>https://github.com/usememos/memos/compare/v0.25.1...v0.25.2</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6927,6 +9222,11 @@
           <t>https://github.com/usememos/memos/compare/v0.26.2...v0.27.0</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6949,6 +9249,11 @@
           <t>https://github.com/usememos/memos/compare/v0.28.0...v0.29.0</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6971,6 +9276,11 @@
           <t>https://github.com/usememos/memos/compare/v0.29.0...v0.29.1</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6993,6 +9303,11 @@
           <t>https://github.com/usememos/memos/compare/v0.29.1...v0.30.0</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7015,6 +9330,11 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.1...3.8.2</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7037,6 +9357,11 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.2.1...3.8.3</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7059,6 +9384,11 @@
           <t>https://github.com/jgm/pandoc/compare/3.9.0.1...3.9.0.2</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7081,6 +9411,11 @@
           <t>https://github.com/jgm/pandoc/compare/3.10.2...3.11</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7103,6 +9438,11 @@
           <t>https://github.com/jgm/pandoc/compare/3.11...3.12</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7125,6 +9465,11 @@
           <t>https://github.com/mermaid-js/mermaid/compare/mermaid@11.13.0...@mermaid-js/tiny@11.13.0</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7147,6 +9492,11 @@
           <t>https://github.com/mermaid-js/mermaid/compare/@mermaid-js/parser@1.1.0...@mermaid-js/tiny@11.14.0</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7169,6 +9519,11 @@
           <t>https://github.com/mermaid-js/mermaid/compare/mermaid@12.0.0...@mermaid-js/examples@2.0.0</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -7191,6 +9546,11 @@
           <t>https://github.com/mermaid-js/mermaid/compare/@mermaid-js/examples@2.0.0...@mermaid-js/mermaid-zenuml@1.0.0</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -7213,6 +9573,11 @@
           <t>https://github.com/mermaid-js/mermaid/compare/@mermaid-js/tiny@12.0.0...@mermaid-js/mermaid-zenuml@1.0.1</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -7235,6 +9600,11 @@
           <t>https://github.com/outline/outline/compare/v0.87.4...v1.0.0</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7257,6 +9627,11 @@
           <t>https://github.com/outline/outline/compare/v1.0.0...v1.0.1</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7279,6 +9654,11 @@
           <t>https://github.com/outline/outline/compare/v1.1.0...v1.2.0</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7301,6 +9681,11 @@
           <t>https://github.com/outline/outline/compare/v1.3.0...v1.4.0</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7323,6 +9708,16 @@
           <t>https://github.com/outline/outline/compare/v1.6.0...v1.6.1</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>mistura fixes com novas ferramentas MCP</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7345,6 +9740,11 @@
           <t>https://github.com/agno-agi/agno/compare/v2.2.7...v2.2.8</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7367,6 +9767,11 @@
           <t>https://github.com/agno-agi/agno/compare/v2.3.5...v2.3.6</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7389,6 +9794,11 @@
           <t>https://github.com/agno-agi/agno/compare/v2.3.14...v2.3.15</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7411,6 +9821,11 @@
           <t>https://github.com/agno-agi/agno/compare/v2.4.2...v2.4.3</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7433,6 +9848,11 @@
           <t>https://github.com/agno-agi/agno/compare/v2.6.18...v2.6.19</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -7455,6 +9875,11 @@
           <t>https://github.com/coder/code-server/compare/v4.117.0...v4.118.0</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -7477,6 +9902,11 @@
           <t>https://github.com/coder/code-server/compare/v4.118.0...v4.121.0</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -7499,6 +9929,11 @@
           <t>https://github.com/coder/code-server/compare/v4.128.0...v4.129.0</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -7521,6 +9956,11 @@
           <t>https://github.com/coder/code-server/compare/v4.132.0...v4.133.0</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7543,6 +9983,11 @@
           <t>https://github.com/coder/code-server/compare/v4.137.0...v4.138.0</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7565,6 +10010,11 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v3.5.6...v3.4.11</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7587,6 +10037,11 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v4.0.1...v3.5.10</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7609,6 +10064,11 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v3.5.11...v4.0.3</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7631,6 +10091,11 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v4.0.5...v4.0.6</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7653,6 +10118,11 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v3.5.14...v4.1.0</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7675,6 +10145,11 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.7.9...v8.7.10</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7697,6 +10172,11 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.1...v8.8.2</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7719,6 +10199,11 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.2...v8.8.3</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -7741,6 +10226,11 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.5...v8.8.6</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7763,6 +10253,11 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.12...v8.8.13</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7785,6 +10280,16 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.2.6...v1.2.7</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>mistura estabilidade, novos provedores e mudancas de ambiente</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7807,6 +10312,11 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.2.8...v1.2.9</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7829,6 +10339,11 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.3.1...v1.3.2</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7851,6 +10366,11 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.3.5...v1.3.6</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7871,6 +10391,11 @@
       <c r="D301" s="2" t="inlineStr">
         <is>
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.3.6...v1.3.7</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
     </row>
